--- a/forms/trg/Formulir_TRG_dims-rg.xlsx
+++ b/forms/trg/Formulir_TRG_dims-rg.xlsx
@@ -967,7 +967,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1340,7 +1340,11 @@
           <t>Master's degree program Communication Sciences, Faculty of Social and Political Sciences, Hasanuddin University</t>
         </is>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>The era of rapid digital transformation has fundamentally reshaped how media operates, how information is produced and consumed, and how society interacts through digital platforms. The Digital Media and Society Research Group (DiMS-RG) at Universitas Hasanuddin was established to address these complex, intersecting challenges through rigorous academic inquiry.</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
